--- a/templates/reg_ocorr_decir.xlsx
+++ b/templates/reg_ocorr_decir.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBC087E-C1EF-41EB-A1C4-C2DE0A4AB1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B83BE39-EC28-4516-9B93-3354B281F1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -737,24 +737,19 @@
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.140625" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="10" customWidth="1"/>
-    <col min="16" max="16" width="8" customWidth="1"/>
-    <col min="17" max="17" width="12" customWidth="1"/>
-    <col min="18" max="18" width="10" customWidth="1"/>
-    <col min="19" max="19" width="8" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="5" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" customWidth="1"/>
+    <col min="7" max="8" width="12.140625" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" customWidth="1"/>
+    <col min="10" max="11" width="12.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" customWidth="1"/>
+    <col min="13" max="14" width="12.140625" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" customWidth="1"/>
+    <col min="16" max="17" width="12.140625" customWidth="1"/>
+    <col min="18" max="18" width="12.85546875" customWidth="1"/>
+    <col min="19" max="19" width="12.140625" customWidth="1"/>
     <col min="20" max="20" width="2.140625" customWidth="1"/>
     <col min="21" max="21" width="9.140625" hidden="1" customWidth="1"/>
     <col min="22" max="16384" width="9.140625" hidden="1"/>
